--- a/web/files/九龙-何文田-耀爵台.xlsx
+++ b/web/files/九龙-何文田-耀爵台.xlsx
@@ -1459,7 +1459,7 @@
           <t>- | 1988呎 (4+房)
 $6550万
 $32,948/呎
-(18年-08月)</t>
+(18年-08月-28日)</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
           <t>- | 982呎 (3房)
 $14461万
 $147,256/呎
-(15年-06月)</t>
+(15年-06月-17日)</t>
         </is>
       </c>
     </row>
@@ -1489,7 +1489,7 @@
           <t>- | 982呎 (3房)
 $14461万
 $147,256/呎
-(15年-06月)</t>
+(15年-06月-17日)</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1534,7 @@
           <t>- | 982呎 (3房)
 $14461万
 $147,256/呎
-(15年-06月)</t>
+(15年-06月-17日)</t>
         </is>
       </c>
     </row>
@@ -1549,7 +1549,7 @@
           <t>- | 982呎 (3房)
 $2050万
 $20,876/呎
-(22年-05月)</t>
+(22年-05月-18日)</t>
         </is>
       </c>
     </row>
@@ -1564,7 +1564,7 @@
           <t>- | 982呎 (3房)
 $2030万
 $20,672/呎
-(21年-01月)</t>
+(21年-01月-06日)</t>
         </is>
       </c>
     </row>
@@ -1594,7 +1594,7 @@
           <t>- | 982呎 (3房)
 $2286万
 $23,279/呎
-(15年-06月)</t>
+(15年-06月-18日)</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
           <t>- | 982呎 (3房)
 $1928万
 $19,633/呎
-(21年-10月)</t>
+(21年-10月-07日)</t>
         </is>
       </c>
     </row>
@@ -1624,7 +1624,7 @@
           <t>- | 982呎 (3房)
 $14461万
 $147,256/呎
-(15年-06月)</t>
+(15年-06月-17日)</t>
         </is>
       </c>
     </row>
@@ -1639,7 +1639,7 @@
           <t>- | 982呎 (3房)
 $14461万
 $147,256/呎
-(15年-06月)</t>
+(15年-06月-17日)</t>
         </is>
       </c>
     </row>
@@ -1654,7 +1654,7 @@
           <t>- | 982呎 (3房)
 $1848万
 $18,819/呎
-(19年-08月)</t>
+(19年-08月-13日)</t>
         </is>
       </c>
     </row>
